--- a/Excelレポート雛形/月次販売計画実績一覧表.template.xlsx
+++ b/Excelレポート雛形/月次販売計画実績一覧表.template.xlsx
@@ -300,7 +300,13 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -646,6 +652,11 @@
   </sheetData>
   <autoFilter ref="A1:J2227"/>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"遅延"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
